--- a/artfynd/A 2554-2022 artfynd.xlsx
+++ b/artfynd/A 2554-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>119235995</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119235997</v>
+        <v>119235996</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560377</v>
+        <v>560256</v>
       </c>
       <c r="R3" t="n">
-        <v>7100333</v>
+        <v>7100312</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119236015</v>
+        <v>119235997</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559895</v>
+        <v>560377</v>
       </c>
       <c r="R4" t="n">
-        <v>7100441</v>
+        <v>7100333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119236011</v>
+        <v>119235999</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560110</v>
+        <v>560261</v>
       </c>
       <c r="R5" t="n">
-        <v>7100352</v>
+        <v>7100362</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119235999</v>
+        <v>119236011</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560261</v>
+        <v>560110</v>
       </c>
       <c r="R6" t="n">
-        <v>7100362</v>
+        <v>7100352</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119236014</v>
+        <v>119236012</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559911</v>
+        <v>560225</v>
       </c>
       <c r="R7" t="n">
-        <v>7100413</v>
+        <v>7100324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119235996</v>
+        <v>119236014</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560256</v>
+        <v>559911</v>
       </c>
       <c r="R8" t="n">
-        <v>7100312</v>
+        <v>7100413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119236012</v>
+        <v>119236015</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560225</v>
+        <v>559895</v>
       </c>
       <c r="R9" t="n">
-        <v>7100324</v>
+        <v>7100441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,12 +1454,7 @@
         <v>119236001</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 2554-2022 artfynd.xlsx
+++ b/artfynd/A 2554-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119235995</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119235996</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119235997</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119235999</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119236011</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119236012</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119236014</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119236015</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,8 +1595,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119236001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>